--- a/extenbooks/S402_extenbook.xlsx
+++ b/extenbooks/S402_extenbook.xlsx
@@ -4285,7 +4285,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -5373,11 +5373,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5400,76 +5400,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Per-hour-wage twin of S401 (Fig 4.17).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S402_research.json", "adequacy_report": "Technical/docs/chapters/CH4_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S402_DPR.md", "epr": "Technical/docs/series/S402_EPR.md", "loader": "Technical/code/L01_loaders/L01_S402_load.py", "processor": "Technical/code/P02_processors/P02_S402_construct.py", "validator": "Technical/code/V03_validators/V03_S402_validate.py", "processed": "Technical/data/processed/S402.parquet", "chopped_csv": "Technical/chopped/S402.csv", "extenbook_xlsx": "Technical/extenbooks/S402_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-18T21:57:52.480731+00:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S402_extenbook.xlsx
+++ b/extenbooks/S402_extenbook.xlsx
@@ -4264,14 +4264,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>**Data Provenance Record (DPR)**</t>
+          <t>**Data Provenance Record (DPR)** — the internal, full-provenance companion to the public Explainer.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Record type**: Data Provenance Record (source-and-construction detail)</t>
         </is>
       </c>
     </row>
@@ -4299,7 +4299,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-ch4-fanout</t>
+          <t>**Prepared by**: RSCD data-construction pipeline</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>- Research dossier: `Technical/research/S402_research.json`</t>
+          <t>- Series research notes: `Technical/research/S402_research.json`</t>
         </is>
       </c>
     </row>
@@ -4435,7 +4435,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>| **S402-A** | XR rows 0–20 (21 points) | Shaikh, *Capitalism* (2016), Appendix 4.2 Table 4.2.4, per-hour-wage columns | money units per unit of output | Reconstructed CSV `SalvagedInputs/book_data/Reconstructed/Appendix_4_2_Table4.csv`, columns `XR`, `afc`, `ulc`, `avc`, `ac`, `mc` |</t>
+          <t>| **S402-A** (the dataset's data column set) | output rows 0–20 (21 points) | Shaikh, *Capitalism* (2016), Appendix 4.2 Table 4.2.4, per-hour-wage columns | money units per unit of output | Reconstructed CSV `SalvagedInputs/book_data/Reconstructed/Appendix_4_2_Table4.csv`, columns `XR`, `afc`, `ulc`, `avc`, `ac`, `mc` |</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>`derived` / `formula`. Loader consumes the tabulated CSV directly.</t>
+          <t>A `derived` series (built by formula). The data-loading step reads the tabulated table directly.</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4686,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>- **Expected MAE**: 0 — direct CSV round-trip.</t>
+          <t>- **Expected mean absolute error (MAE)**: 0 — a direct round-trip of the same table (via the validation step).</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4716,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>**Phase**: 6 (Extension)</t>
+          <t>**Record type**: Extension Provenance Record</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-ch4-fanout</t>
+          <t>**Author**: RSCD data-construction pipeline</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4804,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>## 3-8. Method / Components / Proxies / Synthetic / Failure / CD2</t>
+          <t>## 3-8. Method / Components / Proxies / Synthetic / Failure / Predecessor</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Same as S401_EPR §9 — a viz-only re-derivation on a finer XR grid is possible in Phase 9 but does not constitute extension.</t>
+          <t>Same as S401_EPR §9 — a visualization-only re-derivation on a finer XR grid is possible in a later chapter-level step but does not constitute extension.</t>
         </is>
       </c>
     </row>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-18T21:59:29.072079+00:00</t>
+          <t>2026-07-02T06:22:33.075732+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S402_extenbook.xlsx
+++ b/extenbooks/S402_extenbook.xlsx
@@ -5358,7 +5358,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-02T06:22:33.075732+00:00</t>
+          <t>2026-07-11T03:44:24.821620+00:00</t>
         </is>
       </c>
     </row>
@@ -5373,11 +5373,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5400,6 +5400,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_4_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Renderable multi-trace cost curve (Shaikh Fig 4.17): the per-hour-wage analogue of S401 \u2014 six cost components (afc, ulc, avc, ac, tc, mc) vs cumulative daily output XR. 6 subseries x 21 points = 126 rows (4 nulls are ac at XR=0, expected). Renders as overlaid x-y cost curves (x = cumulative output XR, 'year' index column 0-9, NOT calendar years). TRIAGE_PRESCREEN EMPTY flag is STALE: L01_S402/P02_S402 exist and replicate.py --series S402 builds the chopped (PASS). Data is a verbatim transcription of Appendix Table 4.2.4 (book pp.772-781), validated to &lt;=0.02 rounding noise. KB note: Appendix 4.2 IS in ch18_appendices.md, so a KB-anchored 'From the book' quote is included.", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S402_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S402_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Per-hour-wage twin of S401 (Fig 4.17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>theoretical</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>money_units_per_unit_output_illustrative</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
